--- a/EKG_Kalite_Yönetim_Sistemi/02_Proje ve Ürün-Proses Yeterliliği/03_CMG3 - PIS, CTF ve Özel Karakteristikler/EKG-TAS-MTR-01_otomotiv_cami_ctf__pis_teknik_kanit_uygunluk_matrisi.xlsx
+++ b/EKG_Kalite_Yönetim_Sistemi/02_Proje ve Ürün-Proses Yeterliliği/03_CMG3 - PIS, CTF ve Özel Karakteristikler/EKG-TAS-MTR-01_otomotiv_cami_ctf__pis_teknik_kanit_uygunluk_matrisi.xlsx
@@ -956,7 +956,8 @@
   <pageSetup scale="100"/>
   <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="1">
     <oddHeader>&amp;L&amp;"Arial,Bold"&amp;11EKG-TAS-MTR-01&amp;C&amp;"Arial,Regular"&amp;11Otomotiv Camı CTF / PIS Teknik Kanıt Uygunluk Matrisi</oddHeader>
-    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 04.05.2026 | Revizyon: 19.10.2026&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Arial,Regular"&amp;11İlk Yayın: 02.06.2026 | Revizyon: 03.09.2026
+Revizyon nedeni: Yanlış demiryolu kapsamı kaldırıldı; otomotiv camı CTF/PIS teknik gereklilik ve kanıt matrisi oluşturuldu.&amp;R&amp;11Sayfa &amp;P / &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
 </file>